--- a/model/Модель_расчёт_v2.xlsx
+++ b/model/Модель_расчёт_v2.xlsx
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="851">
   <si>
     <t xml:space="preserve">Книга «Модель расчёт v2» — стационарная часть математической модели местной вытяжной вентиляции сварочного участка</t>
   </si>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">9 Результаты смены — итоги динамического расчёта 8-часовой смены (в Excel их не повторить: нужен шаг по времени 1 с × 28 800 шагов, это делает ядро).</t>
   </si>
   <si>
-    <t xml:space="preserve">10 Регулирование — пусконаладка (почему углы 0/5/8°), один шаг ПИ-регулятора заслонки с подстановкой, правило частотника, скорость привода.</t>
+    <t xml:space="preserve">10 Регулирование — пусконаладка предлагаемой системы (почему углы 0/5/8°) и стандарта (углы при номинальной частоте), один шаг ПИ-регулятора заслонки с подстановкой, правило частотника, скорость привода.</t>
   </si>
   <si>
     <t xml:space="preserve">11 Динамика — как растёт концентрация в цехе после включения постов: C(t), постоянная времени τ = V/L. Зачем нужны размеры цеха.</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">СанПиН, СП 131.13330.2025</t>
   </si>
   <si>
-    <t xml:space="preserve">Без регулирования: всё работает всю смену на расчётном расходе</t>
+    <t xml:space="preserve">Стандарт (без регулирования): заслонки зажаты на углах наладки, вентилятор на номинальных оборотах — местные отсосы тянут 4500 м³/ч всю смену, общеобменная постоянная</t>
   </si>
   <si>
     <t xml:space="preserve">Весь удаляемый воздух</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">Q = Φ·t_см</t>
   </si>
   <si>
-    <t xml:space="preserve">Сверка с ядром: режим «без регулирования» лист 9.</t>
+    <t xml:space="preserve">Сверка с ядром: стандарт, лист 9.</t>
   </si>
   <si>
     <t xml:space="preserve">Тепло за отопительный период (1 смена/сут)</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">ядро (sim.ts)</t>
   </si>
   <si>
-    <t xml:space="preserve">Местные отсосы, средний расход: «открыто/закрыто» + ПЧ</t>
+    <t xml:space="preserve">Местные отсосы, средний расход: «открыто/закрыто» + ПЧ (для справки)</t>
   </si>
   <si>
     <t xml:space="preserve">L̄_мо</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">Меньше, чем у «открыто/закрыто», потому что нет перерасхода сверх 1500 м³/ч.</t>
   </si>
   <si>
-    <t xml:space="preserve">Тепло за смену: «открыто/закрыто» + ПЧ</t>
+    <t xml:space="preserve">Тепло за смену: «открыто/закрыто» + ПЧ (для справки)</t>
   </si>
   <si>
     <t xml:space="preserve">Q = ρ·c·(L̄_оо + L̄_мо)·Δt·t_см/3600</t>
@@ -1901,7 +1901,34 @@
     <t xml:space="preserve">Электроэнергия вентилятора местной вытяжки за смену</t>
   </si>
   <si>
-    <t xml:space="preserve">Без регулирования (режим наладки всю смену)</t>
+    <t xml:space="preserve">Стандарт: номинальная частота вентилятора</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_ном</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p(Q_треб, n_ном) = 1,1·p_треб</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вентилятор подобран с запасом 10 % по давлению и всю смену крутится на номинальных оборотах (демо-характеристика пересчитана по законам подобия, лист 6).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ядро (scenario.ts)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стандарт: давление вентилятора (заслонки на углах наладки)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лишние 10 % давления гасятся заслонками всех постов (углы — лист 10, раздел А2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стандарт: электрическая мощность вентилятора</t>
+  </si>
+  <si>
+    <t xml:space="preserve">С КПД двигателя; частотника нет.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стандарт (без регулирования), энергия за смену</t>
   </si>
   <si>
     <t xml:space="preserve">E</t>
@@ -1910,10 +1937,10 @@
     <t xml:space="preserve">E = P_эл·t_см</t>
   </si>
   <si>
-    <t xml:space="preserve">Вентилятор всю смену работает в режиме листа 6. В ядре чуть меньше — первые 10 с идёт разгон.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">С регулированием мощность меняется каждую секунду (посты включаются и выключаются), энергия = Σ P_эл(tᵢ)·Δt по 28 800 шагам — только в ядре: «открыто/закрыто» 5,39 кВт·ч, предлагаемая 4,97 кВт·ч (лист 9).</t>
+    <t xml:space="preserve">Мощность постоянна всю смену. В ядре чуть меньше — первые 10 с идёт разгон.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">С регулированием мощность меняется каждую секунду (посты включаются и выключаются), энергия = Σ P_эл(tᵢ)·Δt по 28 800 шагам — только в ядре: предлагаемая 4,97 кВт·ч, «открыто/закрыто» + ПЧ (для справки) 5,39 кВт·ч (лист 9),</t>
   </si>
   <si>
     <t xml:space="preserve">Сверка: Excel против расчётного ядра</t>
@@ -1961,16 +1988,16 @@
     <t xml:space="preserve">Электрическая мощность, Вт</t>
   </si>
   <si>
-    <t xml:space="preserve">Тепло за смену без регулирования, кВт·ч</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тепло за смену, «открыто/закрыто» + ПЧ, кВт·ч</t>
+    <t xml:space="preserve">Тепло за смену, стандарт (без регулирования), кВт·ч</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тепло за смену, «открыто/закрыто» + ПЧ (для справки), кВт·ч</t>
   </si>
   <si>
     <t xml:space="preserve">Тепло за смену, предлагаемая система, кВт·ч</t>
   </si>
   <si>
-    <t xml:space="preserve">Электроэнергия за смену без регулирования, кВт·ч</t>
+    <t xml:space="preserve">Электроэнергия за смену, стандарт (без регулирования), кВт·ч</t>
   </si>
   <si>
     <t xml:space="preserve">ПИ-шаг: ζ заслонки при 30°</t>
@@ -1985,7 +2012,7 @@
     <t xml:space="preserve">Объём цеха, м³</t>
   </si>
   <si>
-    <t xml:space="preserve">Тепло и энергия за смену в ядре — интеграл за 8 ч (шаг 1 с); энергия без регулирования в ядре на 0,02 % меньше из-за разгона вентилятора в первые 10 с.</t>
+    <t xml:space="preserve">Тепло и энергия за смену в ядре — интеграл за 8 ч (шаг 1 с); энергия стандарта в ядре на 0,02 % меньше из-за разгона вентилятора в первые 10 с.</t>
   </si>
   <si>
     <t xml:space="preserve">Наибольшее расхождение потерь по элементу, Па</t>
@@ -2018,7 +2045,7 @@
     <t xml:space="preserve">Динамика C(t): наибольшая относит. разница с ядром</t>
   </si>
   <si>
-    <t xml:space="preserve">Итоги динамического расчёта смены 8 ч (ядро, шаг 1 с) — версия 1.7 от 11.10.2026 (фасонные элементы по Идельчику: отводы с k_Re·k_Δ, заслонка — диагр. 9-17, диффузор — диагр. 5-2)</t>
+    <t xml:space="preserve">Итоги динамического расчёта смены 8 ч (ядро, шаг 1 с) — версия 1.9 от 16.10.2026: стандарт = без регулирования (заслонки на углах наладки, вентилятор с запасом 10 % на номинальных оборотах); блок Б — расчёт 11.10.2026 (стандарт в нём не участвует)</t>
   </si>
   <si>
     <t xml:space="preserve">Эти числа получены программой: расписание сварки, регуляторы, приводы заслонок с ограниченной скоростью, частотник, решение сети на каждом шаге, нестационарная концентрация в цехе. В Excel повторить нельзя; проверяемые части (выделения, СП 60, потери, вентилятор, тепло) — на листах 2–7.</t>
@@ -2051,57 +2078,60 @@
     <t xml:space="preserve">Mn макс., мг/м³</t>
   </si>
   <si>
-    <t xml:space="preserve">Без регулирования</t>
+    <t xml:space="preserve">Стандарт: без регулирования (углы наладки, n_ном)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,0 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Открыто/закрыто» + ПЧ (для справки)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,6 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38,4 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Предлагаемая (ПИ по ln ζ + сброс давления)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,3 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,6 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Предлагаемая + ОВ по числу постов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Б. 3 поста, ток меняется 175/225/270 А; режимы общеобменной (местная — предлагаемая)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Режим ОВ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ср. ОВ, м³/ч</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Эл. МВВ+ОВ, кВт·ч</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mn ср.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mn макс.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Время &gt; ПДК</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Постоянный (расчётный, 270 А)</t>
   </si>
   <si>
     <t xml:space="preserve">0 %</t>
   </si>
   <si>
-    <t xml:space="preserve">«Открыто/закрыто» + ПЧ (пром. стандарт)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,6 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38,4 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Предлагаемая (ПИ по ln ζ + сброс давления)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,3 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,6 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Предлагаемая + ОВ по числу постов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Б. 3 поста, ток меняется 175/225/270 А; режимы общеобменной (местная — предлагаемая)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Режим ОВ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ср. ОВ, м³/ч</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Эл. МВВ+ОВ, кВт·ч</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mn ср.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mn макс.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Время &gt; ПДК</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Постоянный (расчётный, 270 А)</t>
-  </si>
-  <si>
     <t xml:space="preserve">По числу работающих постов</t>
   </si>
   <si>
@@ -2138,10 +2168,10 @@
     <t xml:space="preserve">max Σ C/ПДК</t>
   </si>
   <si>
-    <t xml:space="preserve">Без регулирования / пост.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Открыто/закрыто» + ПЧ / пост.</t>
+    <t xml:space="preserve">Стандарт: без регулирования / пост.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Открыто/закрыто» + ПЧ (для справки) / пост.</t>
   </si>
   <si>
     <t xml:space="preserve">Предлагаемая / пост.</t>
@@ -2159,10 +2189,10 @@
     <t xml:space="preserve">то же, цель 0,9</t>
   </si>
   <si>
-    <t xml:space="preserve">ВЫВОДЫ (v1.7, 11.10.2026):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Основная экономия электроэнергии — от регулирования местной вытяжки: «открыто/закрыто» + ПЧ даёт −64 % против работы без регулирования (15,06 → 5,39 кВт·ч); предлагаемая система — ещё −8 % (4,97) и, главное, точность: перерасход 2,6 % времени против 38,4 %.</t>
+    <t xml:space="preserve">ВЫВОДЫ (v1.9, 16.10.2026):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1, Против стандарта (без регулирования) предлагаемая система снижает электроэнергию вентилятора местной вытяжки на 70 % (16,48 → 4,97 кВт·ч) и тепло на 22 % (665 → 519 кВт·ч): простаивающие посты закрыты, обороты снижены, Для справки, против «открыто/закрыто» + ПЧ — ещё −8 % электроэнергии и точность: перерасход 2,6 % времени против 38,4 %,</t>
   </si>
   <si>
     <t xml:space="preserve">2. Общеобменная по потребности — компромисс «тепло ↔ запас по ПДК». При той же безопасности, что у постоянной (max Σ C/ПДК ≈ 0,70), экономия тепла всего −2 % (163 → 160 кВт·ч, таблица В); при допуске до 0,9 ПДК — −14 % (140 кВт·ч).</t>
@@ -2262,6 +2292,63 @@
   </si>
   <si>
     <t xml:space="preserve">Сумма потерь по пути каждого поста одинакова (800,7 Па, лист 5) — у ближних постов труба короче, разницу «съедает» заслонка.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">А2. Пусконаладка стандарта (без регулирования): вентилятор с запасом 10 % на номинальных оборотах, заслонки зажаты так, чтобы каждый пост получил 1500 м³/ч</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Требуемое давление сети при 3 × 1500 м³/ч</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_треб</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Критическая заслонка открыта (режим листа 5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Запас по давлению при подборе вентилятора</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k_зап</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Принятая практика проектирования [Д]; численного запаса в СП 60.13330.2020 нет — источник уточняется.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Номинальная частота</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p(Q_треб, n_ном) = k_зап·p_треб</t>
+  </si>
+  <si>
+    <t xml:space="preserve">лист 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пост 1: угол заслонки стандарта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Не меняется всю смену. Заслонка гасит лишние 10 % давления.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ядро (балансировка при n_ном)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пост 1: расход</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пост 2: угол заслонки стандарта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пост 2: расход</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пост 3: угол заслонки стандарта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пост 3: расход</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стандарт тянет 1500 м³/ч на каждый пост и в паузах между швами: заслонки не закрываются, обороты не снижаются. Предлагаемая система закрывает простаивающие посты и снижает обороты.</t>
   </si>
   <si>
     <t xml:space="preserve">Б. Один шаг ПИ-регулятора заслонки (интегральный закон в пространстве ln ζ)</t>
@@ -2762,7 +2849,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="65">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2976,6 +3063,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3476,12 +3571,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3489,21 +3584,21 @@
         <v>112</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>603</v>
+        <v>612</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="B5" s="45" t="n">
         <f aca="false">'2 Выделения'!$D$6</f>
@@ -3523,7 +3618,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="B6" s="45" t="n">
         <f aca="false">'2 Выделения'!$D$7</f>
@@ -3543,7 +3638,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="B7" s="45" t="n">
         <f aca="false">'3 СП 60'!$D$10</f>
@@ -3563,7 +3658,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="B8" s="45" t="n">
         <f aca="false">'3 СП 60'!$D$11</f>
@@ -3583,7 +3678,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="B9" s="45" t="n">
         <f aca="false">'6 Вентилятор'!$D$16</f>
@@ -3603,7 +3698,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="B10" s="45" t="n">
         <f aca="false">'6 Вентилятор'!$D$20</f>
@@ -3623,7 +3718,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="B11" s="45" t="n">
         <f aca="false">'6 Вентилятор'!$D$27</f>
@@ -3643,7 +3738,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="B12" s="45" t="n">
         <f aca="false">'6 Вентилятор'!$D$32</f>
@@ -3663,7 +3758,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="22" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="B13" s="45" t="n">
         <f aca="false">'6 Вентилятор'!$D$38</f>
@@ -3683,18 +3778,18 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="B14" s="45" t="n">
         <f aca="false">'7 Тепло'!$D$9</f>
         <v>665.306082898869</v>
       </c>
       <c r="C14" s="46" t="n">
-        <v>665.195734580434</v>
+        <v>665.190604268625</v>
       </c>
       <c r="D14" s="47" t="n">
         <f aca="false">ABS(B14-C14)/ABS(C14)</f>
-        <v>0.000165888493714971</v>
+        <v>0.000173602317144418</v>
       </c>
       <c r="E14" s="21" t="str">
         <f aca="false">IF(D14&lt;0.001,"ОК","ПРОВЕРИТЬ")</f>
@@ -3703,7 +3798,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="22" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="B15" s="45" t="n">
         <f aca="false">'7 Тепло'!$D$18</f>
@@ -3723,7 +3818,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="B16" s="45" t="n">
         <f aca="false">'7 Тепло'!$D$19</f>
@@ -3743,18 +3838,18 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="22" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="B17" s="45" t="n">
-        <f aca="false">'7 Тепло'!$D$21</f>
-        <v>15.0590604704643</v>
+        <f aca="false">'7 Тепло'!$D$24</f>
+        <v>16.487584096</v>
       </c>
       <c r="C17" s="46" t="n">
-        <v>15.0566179832324</v>
+        <v>16.4847439364815</v>
       </c>
       <c r="D17" s="47" t="n">
         <f aca="false">ABS(B17-C17)/ABS(C17)</f>
-        <v>0.000162220176837712</v>
+        <v>0.000172290181117913</v>
       </c>
       <c r="E17" s="21" t="str">
         <f aca="false">IF(D17&lt;0.001,"ОК","ПРОВЕРИТЬ")</f>
@@ -3763,10 +3858,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="B18" s="45" t="n">
-        <f aca="false">'10 Регулирование'!$D$25</f>
+        <f aca="false">'10 Регулирование'!$D$36</f>
         <v>4.5</v>
       </c>
       <c r="C18" s="46" t="n">
@@ -3783,10 +3878,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="22" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="B19" s="45" t="n">
-        <f aca="false">'10 Регулирование'!$D$28</f>
+        <f aca="false">'10 Регулирование'!$D$39</f>
         <v>2.78452526312763</v>
       </c>
       <c r="C19" s="46" t="n">
@@ -3803,10 +3898,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="B20" s="45" t="n">
-        <f aca="false">'10 Регулирование'!$D$29</f>
+        <f aca="false">'10 Регулирование'!$D$40</f>
         <v>25.5236198173473</v>
       </c>
       <c r="C20" s="46" t="n">
@@ -3823,7 +3918,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="22" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="B21" s="45" t="n">
         <f aca="false">'11 Динамика'!$D$5</f>
@@ -3843,19 +3938,19 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="B23" s="48" t="n">
         <f aca="false">'5 Потери'!$R$51</f>
         <v>5.44444446859416E-006</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="E23" s="21" t="str">
         <f aca="false">IF(ABS(B23)&lt;=0.001,"ОК","ПРОВЕРИТЬ")</f>
@@ -3864,14 +3959,14 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="B24" s="48" t="n">
         <f aca="false">'6 Вентилятор'!$D$22</f>
         <v>-2.52090870844768E-005</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="E24" s="21" t="str">
         <f aca="false">IF(ABS(B24)&lt;=0.01,"ОК","ПРОВЕРИТЬ")</f>
@@ -3880,14 +3975,14 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="B25" s="48" t="n">
         <f aca="false">'6 Вентилятор'!$D$23</f>
         <v>-2.8875702582809E-005</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="E25" s="21" t="str">
         <f aca="false">IF(ABS(B25)&lt;=0.01,"ОК","ПРОВЕРИТЬ")</f>
@@ -3896,14 +3991,14 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="B26" s="48" t="n">
         <f aca="false">'6 Вентилятор'!$D$24</f>
         <v>-2.40522252852315E-005</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="E26" s="21" t="str">
         <f aca="false">IF(ABS(B26)&lt;=0.01,"ОК","ПРОВЕРИТЬ")</f>
@@ -3912,14 +4007,14 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="B27" s="48" t="n">
         <f aca="false">'2 Выделения'!$D$13</f>
         <v>0</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="E27" s="21" t="str">
         <f aca="false">IF(ABS(B27)&lt;=0.000000001,"ОК","ПРОВЕРИТЬ")</f>
@@ -3928,14 +4023,14 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>632</v>
+        <v>641</v>
       </c>
       <c r="B28" s="48" t="n">
         <f aca="false">'3 СП 60'!$D$13-'1 Исходные'!$D$25</f>
         <v>0</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="E28" s="21" t="str">
         <f aca="false">IF(ABS(B28)&lt;=0.000000001,"ОК","ПРОВЕРИТЬ")</f>
@@ -3944,14 +4039,14 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="22" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="B29" s="48" t="n">
         <f aca="false">MAX('11 Динамика'!$E$13:$E$28)</f>
         <v>8.53793584632849E-005</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="E29" s="21" t="str">
         <f aca="false">IF(ABS(B29)&lt;=0.001,"ОК","ПРОВЕРИТЬ")</f>
@@ -3983,12 +4078,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -4001,41 +4096,41 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>636</v>
+        <v>645</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="B6" s="24" t="n">
-        <v>15.06</v>
+        <v>16.48</v>
       </c>
       <c r="C6" s="24" t="n">
         <v>665</v>
@@ -4044,10 +4139,10 @@
         <v>4498</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="G6" s="24" t="n">
         <v>0.064</v>
@@ -4058,7 +4153,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="B7" s="24" t="n">
         <v>5.39</v>
@@ -4070,10 +4165,10 @@
         <v>1872</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="G7" s="24" t="n">
         <v>0.084</v>
@@ -4084,7 +4179,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="B8" s="24" t="n">
         <v>4.97</v>
@@ -4096,10 +4191,10 @@
         <v>1727</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="G8" s="24" t="n">
         <v>0.087</v>
@@ -4110,7 +4205,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="B9" s="24" t="n">
         <v>4.97</v>
@@ -4122,10 +4217,10 @@
         <v>1727</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="G9" s="24" t="n">
         <v>0.107</v>
@@ -4136,36 +4231,36 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>654</v>
+        <v>663</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="H12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="B13" s="24" t="n">
         <v>10847</v>
@@ -4183,13 +4278,13 @@
         <v>0.096</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="H13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="B14" s="24" t="n">
         <v>5344</v>
@@ -4207,13 +4302,13 @@
         <v>0.143</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="H14" s="24"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="B15" s="24" t="n">
         <v>7538</v>
@@ -4231,13 +4326,13 @@
         <v>0.111</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="H15" s="24"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>664</v>
+        <v>674</v>
       </c>
       <c r="B16" s="24" t="n">
         <v>6879</v>
@@ -4255,13 +4350,13 @@
         <v>0.115</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="H16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="B17" s="24" t="n">
         <v>4160</v>
@@ -4279,13 +4374,13 @@
         <v>0.154</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="H17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="B18" s="24" t="n">
         <v>10847</v>
@@ -4303,13 +4398,13 @@
         <v>0.137</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="H18" s="24"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="24" t="s">
-        <v>667</v>
+        <v>677</v>
       </c>
       <c r="B19" s="24" t="n">
         <v>5344</v>
@@ -4327,13 +4422,13 @@
         <v>0.205</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="H19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="B20" s="24" t="n">
         <v>7538</v>
@@ -4351,13 +4446,13 @@
         <v>0.159</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="H20" s="24"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="24" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="B21" s="24" t="n">
         <v>11011</v>
@@ -4375,30 +4470,30 @@
         <v>0.123</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="H21" s="24"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
@@ -4406,10 +4501,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="24" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="B25" s="24" t="n">
-        <v>20.58</v>
+        <v>24.21</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>341</v>
@@ -4418,32 +4513,32 @@
         <v>962</v>
       </c>
       <c r="E25" s="24" t="n">
-        <v>0.382</v>
+        <v>0.381</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="24" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="B26" s="24" t="n">
-        <v>7.7</v>
+        <v>7.96</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>962</v>
       </c>
       <c r="E26" s="24" t="n">
-        <v>0.649</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="24" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="B27" s="24" t="n">
-        <v>6.62</v>
+        <v>6.89</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>163</v>
@@ -4452,32 +4547,32 @@
         <v>962</v>
       </c>
       <c r="E27" s="24" t="n">
-        <v>0.708</v>
+        <v>0.704</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="24" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="B28" s="24" t="n">
-        <v>6.62</v>
+        <v>6.89</v>
       </c>
       <c r="C28" s="24" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D28" s="24" t="n">
         <v>486</v>
       </c>
       <c r="E28" s="24" t="n">
-        <v>0.774</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="24" t="s">
-        <v>678</v>
+        <v>688</v>
       </c>
       <c r="B29" s="24" t="n">
-        <v>6.62</v>
+        <v>6.89</v>
       </c>
       <c r="C29" s="24" t="n">
         <v>283</v>
@@ -4486,32 +4581,32 @@
         <v>3240</v>
       </c>
       <c r="E29" s="24" t="n">
-        <v>0.474</v>
+        <v>0.471</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="24" t="s">
-        <v>679</v>
+        <v>689</v>
       </c>
       <c r="B30" s="24" t="n">
-        <v>6.62</v>
+        <v>6.89</v>
       </c>
       <c r="C30" s="24" t="n">
         <v>160</v>
       </c>
       <c r="D30" s="24" t="n">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="E30" s="24" t="n">
-        <v>0.696</v>
+        <v>0.691</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="24" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="B31" s="24" t="n">
-        <v>6.62</v>
+        <v>6.89</v>
       </c>
       <c r="C31" s="24" t="n">
         <v>140</v>
@@ -4520,12 +4615,12 @@
         <v>526</v>
       </c>
       <c r="E31" s="24" t="n">
-        <v>0.752</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="49" t="s">
-        <v>681</v>
+        <v>691</v>
       </c>
       <c r="B33" s="49"/>
       <c r="C33" s="49"/>
@@ -4538,7 +4633,7 @@
     </row>
     <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="50" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="B34" s="50"/>
       <c r="C34" s="50"/>
@@ -4551,7 +4646,7 @@
     </row>
     <row r="35" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="50" t="s">
-        <v>683</v>
+        <v>693</v>
       </c>
       <c r="B35" s="50"/>
       <c r="C35" s="50"/>
@@ -4564,7 +4659,7 @@
     </row>
     <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="50" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
       <c r="B36" s="50"/>
       <c r="C36" s="50"/>
@@ -4577,7 +4672,7 @@
     </row>
     <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="50" t="s">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="B37" s="50"/>
       <c r="C37" s="50"/>
@@ -4590,7 +4685,7 @@
     </row>
     <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="50" t="s">
-        <v>686</v>
+        <v>696</v>
       </c>
       <c r="B38" s="50"/>
       <c r="C38" s="50"/>
@@ -4603,7 +4698,7 @@
     </row>
     <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="50" t="s">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="B39" s="50"/>
       <c r="C39" s="50"/>
@@ -4616,7 +4711,7 @@
     </row>
     <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="50" t="s">
-        <v>688</v>
+        <v>698</v>
       </c>
       <c r="B40" s="50"/>
       <c r="C40" s="50"/>
@@ -4654,7 +4749,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -4669,12 +4764,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -4712,7 +4807,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -4727,24 +4822,24 @@
         <v>1</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
       <c r="D6" s="51" t="n">
         <f aca="false">'5 Потери'!$J$9</f>
         <v>0.121757</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>696</v>
+        <v>706</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4752,7 +4847,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>361</v>
@@ -4765,11 +4860,11 @@
         <v>123</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4777,10 +4872,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="D8" s="52" t="n">
         <f aca="false">'5 Потери'!$R$9</f>
@@ -4790,7 +4885,7 @@
         <v>496</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8" t="s">
@@ -4802,10 +4897,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="D9" s="53" t="n">
         <f aca="false">'5 Потери'!$R$9-INDEX('4 Таблицы'!$B$5:$B$13,1)*'5 Потери'!$Q$9</f>
@@ -4815,10 +4910,10 @@
         <v>496</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="H9" s="8"/>
     </row>
@@ -4827,24 +4922,24 @@
         <v>5</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>707</v>
+        <v>717</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
       <c r="D10" s="51" t="n">
         <f aca="false">'5 Потери'!$J$19</f>
         <v>5.21025</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>696</v>
+        <v>706</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4852,7 +4947,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>361</v>
@@ -4865,11 +4960,11 @@
         <v>123</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="8" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4877,10 +4972,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>709</v>
+        <v>719</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="D12" s="52" t="n">
         <f aca="false">'5 Потери'!$R$19</f>
@@ -4890,7 +4985,7 @@
         <v>496</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8" t="s">
@@ -4902,10 +4997,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="D13" s="53" t="n">
         <f aca="false">'5 Потери'!$R$19-INDEX('4 Таблицы'!$B$5:$B$13,1)*'5 Потери'!$Q$19</f>
@@ -4915,10 +5010,10 @@
         <v>496</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="H13" s="8"/>
     </row>
@@ -4927,24 +5022,24 @@
         <v>9</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
       <c r="D14" s="51" t="n">
         <f aca="false">'5 Потери'!$J$28</f>
         <v>7.990537</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="8" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>696</v>
+        <v>706</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4952,7 +5047,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>361</v>
@@ -4965,11 +5060,11 @@
         <v>123</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4977,10 +5072,10 @@
         <v>11</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>713</v>
+        <v>723</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="D16" s="52" t="n">
         <f aca="false">'5 Потери'!$R$28</f>
@@ -4990,7 +5085,7 @@
         <v>496</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="8" t="s">
@@ -5002,10 +5097,10 @@
         <v>12</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>714</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>704</v>
       </c>
       <c r="D17" s="53" t="n">
         <f aca="false">'5 Потери'!$R$28-INDEX('4 Таблицы'!$B$5:$B$13,1)*'5 Потери'!$Q$28</f>
@@ -5015,16 +5110,16 @@
         <v>496</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="H17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="10" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -5035,7 +5130,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -5045,29 +5140,28 @@
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
         <v>13</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>718</v>
-      </c>
-      <c r="D20" s="54" t="n">
-        <f aca="false">'1 Исходные'!$D$17</f>
-        <v>1500</v>
+        <v>728</v>
+      </c>
+      <c r="D20" s="43" t="n">
+        <v>800.70062</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>167</v>
+        <v>496</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8" t="s">
-        <v>719</v>
+        <v>729</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>720</v>
+        <v>483</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5075,23 +5169,23 @@
         <v>14</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>1320</v>
+        <v>731</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>1.1</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>167</v>
+        <v>123</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="8" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>723</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5099,21 +5193,24 @@
         <v>15</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>724</v>
+        <v>733</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>725</v>
-      </c>
-      <c r="D22" s="15" t="n">
-        <v>30</v>
+        <v>596</v>
+      </c>
+      <c r="D22" s="52" t="n">
+        <f aca="false">'7 Тепло'!$D$21</f>
+        <v>1462.102749</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>694</v>
-      </c>
-      <c r="F22" s="8"/>
+        <v>479</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>734</v>
+      </c>
       <c r="G22" s="8"/>
       <c r="H22" s="8" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5121,23 +5218,23 @@
         <v>16</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>726</v>
+        <v>736</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="D23" s="15" t="n">
-        <v>4</v>
+        <v>703</v>
+      </c>
+      <c r="D23" s="54" t="n">
+        <v>15.66483</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>728</v>
+        <v>704</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="8" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5145,46 +5242,45 @@
         <v>17</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>548</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>1</v>
+        <v>485</v>
+      </c>
+      <c r="D24" s="55" t="n">
+        <v>1499.332214</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>732</v>
+        <v>167</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
         <v>18</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>735</v>
-      </c>
-      <c r="D25" s="38" t="n">
-        <f aca="false">IF('10 Регулирование'!$D$22&gt;=90,10000,EXP(LN(INDEX('4 Таблицы'!$B$5:$B$13,MATCH('10 Регулирование'!$D$22,'4 Таблицы'!$A$5:$A$13,1)))+('10 Регулирование'!$D$22-INDEX('4 Таблицы'!$A$5:$A$13,MATCH('10 Регулирование'!$D$22,'4 Таблицы'!$A$5:$A$13,1)))/(INDEX('4 Таблицы'!$A$5:$A$13,MATCH('10 Регулирование'!$D$22,'4 Таблицы'!$A$5:$A$13,1)+1)-INDEX('4 Таблицы'!$A$5:$A$13,MATCH('10 Регулирование'!$D$22,'4 Таблицы'!$A$5:$A$13,1)))*(LN(INDEX('4 Таблицы'!$B$5:$B$13,MATCH('10 Регулирование'!$D$22,'4 Таблицы'!$A$5:$A$13,1)+1))-LN(INDEX('4 Таблицы'!$B$5:$B$13,MATCH('10 Регулирование'!$D$22,'4 Таблицы'!$A$5:$A$13,1))))))</f>
-        <v>4.5</v>
+        <v>703</v>
+      </c>
+      <c r="D25" s="54" t="n">
+        <v>16.805753</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="G25" s="8"/>
+        <v>704</v>
+      </c>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8" t="s">
+        <v>737</v>
+      </c>
       <c r="H25" s="8" t="s">
-        <v>365</v>
+        <v>738</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5192,356 +5288,355 @@
         <v>19</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>738</v>
-      </c>
-      <c r="D26" s="38" t="n">
-        <f aca="false">('10 Регулирование'!$D$21-'10 Регулирование'!$D$20)/'10 Регулирование'!$D$20</f>
-        <v>-0.12</v>
+        <v>485</v>
+      </c>
+      <c r="D26" s="55" t="n">
+        <v>1499.413924</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>739</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>740</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
       <c r="H26" s="8" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
         <v>20</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>742</v>
-      </c>
-      <c r="D27" s="38" t="n">
-        <f aca="false">'10 Регулирование'!$D$23*'10 Регулирование'!$D$26*'10 Регулирование'!$D$24</f>
-        <v>-0.48</v>
+        <v>703</v>
+      </c>
+      <c r="D27" s="54" t="n">
+        <v>17.616855</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>743</v>
-      </c>
+        <v>704</v>
+      </c>
+      <c r="F27" s="8"/>
       <c r="G27" s="8" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
         <v>21</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>747</v>
-      </c>
-      <c r="D28" s="38" t="n">
-        <f aca="false">EXP(MIN(INDEX('4 Таблицы'!$C$5:$C$13,8),MAX(INDEX('4 Таблицы'!$C$5:$C$13,1),LN('10 Регулирование'!$D$25)+'10 Регулирование'!$D$27)))</f>
-        <v>2.78452526312763</v>
+        <v>485</v>
+      </c>
+      <c r="D28" s="55" t="n">
+        <v>1499.469085</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>748</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="F28" s="8"/>
       <c r="G28" s="8"/>
       <c r="H28" s="8" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>749</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>750</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <f aca="false">IF(LN('10 Регулирование'!$D$28)&gt;=INDEX('4 Таблицы'!$C$5:$C$13,8),70,INDEX('4 Таблицы'!$A$5:$A$13,MATCH(LN('10 Регулирование'!$D$28),'4 Таблицы'!$C$5:$C$13,1))+(LN('10 Регулирование'!$D$28)-INDEX('4 Таблицы'!$C$5:$C$13,MATCH(LN('10 Регулирование'!$D$28),'4 Таблицы'!$C$5:$C$13,1)))/(INDEX('4 Таблицы'!$C$5:$C$13,MATCH(LN('10 Регулирование'!$D$28),'4 Таблицы'!$C$5:$C$13,1)+1)-INDEX('4 Таблицы'!$C$5:$C$13,MATCH(LN('10 Регулирование'!$D$28),'4 Таблицы'!$C$5:$C$13,1)))*(INDEX('4 Таблицы'!$A$5:$A$13,MATCH(LN('10 Регулирование'!$D$28),'4 Таблицы'!$C$5:$C$13,1)+1)-INDEX('4 Таблицы'!$A$5:$A$13,MATCH(LN('10 Регулирование'!$D$28),'4 Таблицы'!$C$5:$C$13,1))))</f>
-        <v>25.5236198173473</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>694</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>751</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>752</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>753</v>
-      </c>
+        <v>483</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>754</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>755</v>
-      </c>
-      <c r="D30" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>732</v>
-      </c>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8" t="s">
-        <v>756</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>757</v>
-      </c>
+      <c r="A30" s="11" t="s">
+        <v>745</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="D31" s="56" t="n">
+        <f aca="false">'1 Исходные'!$D$17</f>
+        <v>1500</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8" t="s">
+        <v>748</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>1320</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B33" s="8" t="s">
+        <v>753</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>755</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>756</v>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="H34" s="8" t="s">
         <v>759</v>
-      </c>
-      <c r="D31" s="55" t="n">
-        <f aca="false">90/'10 Регулирование'!$D$30</f>
-        <v>11.25</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>760</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>761</v>
-      </c>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>762</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>763</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <f aca="false">SIGN('10 Регулирование'!$D$29-'10 Регулирование'!$D$22)*MIN(ABS('10 Регулирование'!$D$29-'10 Регулирование'!$D$22),'10 Регулирование'!$D$31*'10 Регулирование'!$D$24)</f>
-        <v>-4.4763801826527</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>694</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>764</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>765</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11" t="s">
-        <v>766</v>
-      </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>767</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>768</v>
-      </c>
-      <c r="D34" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>694</v>
-      </c>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>770</v>
-      </c>
-      <c r="D35" s="15" t="n">
-        <v>12</v>
+        <v>548</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>694</v>
+        <v>761</v>
       </c>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="8" t="s">
-        <v>723</v>
+        <v>762</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>772</v>
-      </c>
-      <c r="D36" s="15" t="n">
-        <v>15</v>
+        <v>764</v>
+      </c>
+      <c r="D36" s="38" t="n">
+        <f aca="false">IF('10 Регулирование'!$D$33&gt;=90,10000,EXP(LN(INDEX('4 Таблицы'!$B$5:$B$13,MATCH('10 Регулирование'!$D$33,'4 Таблицы'!$A$5:$A$13,1)))+('10 Регулирование'!$D$33-INDEX('4 Таблицы'!$A$5:$A$13,MATCH('10 Регулирование'!$D$33,'4 Таблицы'!$A$5:$A$13,1)))/(INDEX('4 Таблицы'!$A$5:$A$13,MATCH('10 Регулирование'!$D$33,'4 Таблицы'!$A$5:$A$13,1)+1)-INDEX('4 Таблицы'!$A$5:$A$13,MATCH('10 Регулирование'!$D$33,'4 Таблицы'!$A$5:$A$13,1)))*(LN(INDEX('4 Таблицы'!$B$5:$B$13,MATCH('10 Регулирование'!$D$33,'4 Таблицы'!$A$5:$A$13,1)+1))-LN(INDEX('4 Таблицы'!$B$5:$B$13,MATCH('10 Регулирование'!$D$33,'4 Таблицы'!$A$5:$A$13,1))))))</f>
+        <v>4.5</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>694</v>
-      </c>
-      <c r="F36" s="8"/>
+        <v>123</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>765</v>
+      </c>
       <c r="G36" s="8"/>
       <c r="H36" s="8" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>774</v>
-      </c>
-      <c r="D37" s="12" t="n">
-        <v>0</v>
+        <v>767</v>
+      </c>
+      <c r="D37" s="38" t="n">
+        <f aca="false">('10 Регулирование'!$D$32-'10 Регулирование'!$D$31)/'10 Регулирование'!$D$31</f>
+        <v>-0.12</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>123</v>
       </c>
       <c r="F37" s="8" t="s">
+        <v>768</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>769</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>770</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>771</v>
+      </c>
+      <c r="D38" s="38" t="n">
+        <f aca="false">'10 Регулирование'!$D$34*'10 Регулирование'!$D$37*'10 Регулирование'!$D$35</f>
+        <v>-0.48</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" s="8" t="s">
         <v>775</v>
       </c>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="B38" s="8" t="s">
+      <c r="C39" s="8" t="s">
         <v>776</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="D39" s="38" t="n">
+        <f aca="false">EXP(MIN(INDEX('4 Таблицы'!$C$5:$C$13,8),MAX(INDEX('4 Таблицы'!$C$5:$C$13,1),LN('10 Регулирование'!$D$36)+'10 Регулирование'!$D$38)))</f>
+        <v>2.78452526312763</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F39" s="8" t="s">
         <v>777</v>
       </c>
-      <c r="D38" s="53" t="n">
-        <f aca="false">MIN('10 Регулирование'!$D$34,'10 Регулирование'!$D$35,'10 Регулирование'!$D$36)</f>
-        <v>8</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>694</v>
-      </c>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-    </row>
-    <row r="39" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8" t="n">
+      <c r="G39" s="8"/>
+      <c r="H39" s="8" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B40" s="8" t="s">
         <v>778</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C40" s="8" t="s">
         <v>779</v>
       </c>
-      <c r="D39" s="53" t="n">
-        <f aca="false">IF(AND('10 Регулирование'!$D$38&lt;2,'10 Регулирование'!$D$37&gt;0.002),400*'10 Регулирование'!$D$37*'10 Регулирование'!$D$24,IF('10 Регулирование'!$D$38&gt;5,-1*('10 Регулирование'!$D$38-5)*'10 Регулирование'!$D$24,0))</f>
-        <v>-3</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="F39" s="8" t="s">
+      <c r="D40" s="18" t="n">
+        <f aca="false">IF(LN('10 Регулирование'!$D$39)&gt;=INDEX('4 Таблицы'!$C$5:$C$13,8),70,INDEX('4 Таблицы'!$A$5:$A$13,MATCH(LN('10 Регулирование'!$D$39),'4 Таблицы'!$C$5:$C$13,1))+(LN('10 Регулирование'!$D$39)-INDEX('4 Таблицы'!$C$5:$C$13,MATCH(LN('10 Регулирование'!$D$39),'4 Таблицы'!$C$5:$C$13,1)))/(INDEX('4 Таблицы'!$C$5:$C$13,MATCH(LN('10 Регулирование'!$D$39),'4 Таблицы'!$C$5:$C$13,1)+1)-INDEX('4 Таблицы'!$C$5:$C$13,MATCH(LN('10 Регулирование'!$D$39),'4 Таблицы'!$C$5:$C$13,1)))*(INDEX('4 Таблицы'!$A$5:$A$13,MATCH(LN('10 Регулирование'!$D$39),'4 Таблицы'!$C$5:$C$13,1)+1)-INDEX('4 Таблицы'!$A$5:$A$13,MATCH(LN('10 Регулирование'!$D$39),'4 Таблицы'!$C$5:$C$13,1))))</f>
+        <v>25.5236198173473</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="F40" s="8" t="s">
         <v>780</v>
       </c>
-      <c r="G39" s="8" t="s">
+      <c r="G40" s="8" t="s">
         <v>781</v>
       </c>
-      <c r="H39" s="8" t="s">
+      <c r="H40" s="8" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="11" t="s">
-        <v>783</v>
-      </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-    </row>
-    <row r="41" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
         <v>32</v>
       </c>
       <c r="B41" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>784</v>
       </c>
-      <c r="C41" s="8"/>
-      <c r="D41" s="56" t="n">
-        <v>0.018</v>
+      <c r="D41" s="16" t="n">
+        <v>8</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>123</v>
+        <v>761</v>
       </c>
       <c r="F41" s="8"/>
       <c r="G41" s="8" t="s">
@@ -5551,166 +5646,402 @@
         <v>786</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
         <v>33</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>787</v>
       </c>
-      <c r="C42" s="8"/>
+      <c r="C42" s="8" t="s">
+        <v>788</v>
+      </c>
       <c r="D42" s="57" t="n">
-        <v>0.082</v>
+        <f aca="false">90/'10 Регулирование'!$D$41</f>
+        <v>11.25</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8" t="s">
-        <v>788</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>789</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
         <v>34</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>789</v>
-      </c>
-      <c r="C43" s="8"/>
-      <c r="D43" s="56" t="n">
-        <v>0.075</v>
+        <v>791</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <f aca="false">SIGN('10 Регулирование'!$D$40-'10 Регулирование'!$D$33)*MIN(ABS('10 Регулирование'!$D$40-'10 Регулирование'!$D$33),'10 Регулирование'!$D$42*'10 Регулирование'!$D$35)</f>
+        <v>-4.4763801826527</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="F43" s="8"/>
+        <v>704</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>793</v>
+      </c>
       <c r="G43" s="8" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="n">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="11" t="s">
+        <v>795</v>
+      </c>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="B44" s="8" t="s">
-        <v>791</v>
-      </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="57" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8" t="s">
-        <v>788</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8" t="n">
-        <v>36</v>
-      </c>
       <c r="B45" s="8" t="s">
-        <v>792</v>
-      </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="56" t="n">
-        <v>0.191</v>
+        <v>796</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="D45" s="15" t="n">
+        <v>8</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>123</v>
+        <v>704</v>
       </c>
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
       <c r="H45" s="8" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>799</v>
+      </c>
+      <c r="D46" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="B46" s="8" t="s">
-        <v>793</v>
-      </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="57" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8" t="s">
-        <v>788</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="8" t="n">
-        <v>38</v>
-      </c>
       <c r="B47" s="8" t="s">
-        <v>794</v>
-      </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="56" t="n">
-        <v>0.79</v>
+        <v>800</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="D47" s="15" t="n">
+        <v>15</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>123</v>
+        <v>704</v>
       </c>
       <c r="F47" s="8"/>
-      <c r="G47" s="8" t="s">
-        <v>795</v>
-      </c>
+      <c r="G47" s="8"/>
       <c r="H47" s="8" t="s">
-        <v>786</v>
+        <v>752</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>802</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="B48" s="8" t="s">
-        <v>796</v>
-      </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="57" t="n">
+      <c r="B49" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="D49" s="53" t="n">
+        <f aca="false">MIN('10 Регулирование'!$D$45,'10 Регулирование'!$D$46,'10 Регулирование'!$D$47)</f>
+        <v>8</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+    </row>
+    <row r="50" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="D50" s="53" t="n">
+        <f aca="false">IF(AND('10 Регулирование'!$D$49&lt;2,'10 Регулирование'!$D$48&gt;0.002),400*'10 Регулирование'!$D$48*'10 Регулирование'!$D$35,IF('10 Регулирование'!$D$49&gt;5,-1*('10 Регулирование'!$D$49-5)*'10 Регулирование'!$D$35,0))</f>
+        <v>-3</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="11" t="s">
+        <v>812</v>
+      </c>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+    </row>
+    <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="C52" s="8"/>
+      <c r="D52" s="58" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8" t="s">
+        <v>814</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="C53" s="8"/>
+      <c r="D53" s="59" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>818</v>
+      </c>
+      <c r="C54" s="8"/>
+      <c r="D54" s="58" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>820</v>
+      </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="59" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>821</v>
+      </c>
+      <c r="C56" s="8"/>
+      <c r="D56" s="58" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>822</v>
+      </c>
+      <c r="C57" s="8"/>
+      <c r="D57" s="59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>823</v>
+      </c>
+      <c r="C58" s="8"/>
+      <c r="D58" s="58" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8" t="s">
+        <v>824</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>825</v>
+      </c>
+      <c r="C59" s="8"/>
+      <c r="D59" s="59" t="n">
         <v>0.266</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E59" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8" t="s">
-        <v>797</v>
-      </c>
-      <c r="H48" s="8" t="s">
+      <c r="F59" s="8"/>
+      <c r="G59" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="H59" s="8" t="s">
         <v>483</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="B18:H18"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A51:H51"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5742,12 +6073,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>798</v>
+        <v>827</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>799</v>
+        <v>828</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -5801,10 +6132,10 @@
         <v>227</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>800</v>
+        <v>829</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>801</v>
+        <v>830</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>57</v>
@@ -5838,10 +6169,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>802</v>
+        <v>831</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>803</v>
+        <v>832</v>
       </c>
       <c r="D7" s="52" t="n">
         <f aca="false">'2 Выделения'!$D$17</f>
@@ -5861,7 +6192,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>804</v>
+        <v>833</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>296</v>
@@ -5884,10 +6215,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>805</v>
+        <v>834</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>806</v>
+        <v>835</v>
       </c>
       <c r="D9" s="18" t="n">
         <f aca="false">'11 Динамика'!$D$5/'11 Динамика'!$D$6</f>
@@ -5897,13 +6228,13 @@
         <v>223</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>807</v>
+        <v>836</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>809</v>
+        <v>838</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5911,17 +6242,17 @@
         <v>6</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>810</v>
+        <v>839</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>806</v>
+        <v>835</v>
       </c>
       <c r="D10" s="52" t="n">
         <f aca="false">'11 Динамика'!$D$9*60</f>
         <v>78.9852046129388</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>811</v>
+        <v>840</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -5932,10 +6263,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>812</v>
+        <v>841</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>813</v>
+        <v>842</v>
       </c>
       <c r="D11" s="38" t="n">
         <f aca="false">'11 Динамика'!$D$8+'11 Динамика'!$D$7/'11 Динамика'!$D$6</f>
@@ -5945,353 +6276,353 @@
         <v>192</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>815</v>
+        <v>844</v>
       </c>
       <c r="H11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="58" t="s">
-        <v>816</v>
-      </c>
-      <c r="C12" s="58" t="s">
-        <v>817</v>
-      </c>
-      <c r="D12" s="58" t="s">
-        <v>818</v>
-      </c>
-      <c r="E12" s="58" t="s">
-        <v>819</v>
-      </c>
-      <c r="F12" s="58" t="s">
-        <v>820</v>
+      <c r="B12" s="60" t="s">
+        <v>845</v>
+      </c>
+      <c r="C12" s="60" t="s">
+        <v>846</v>
+      </c>
+      <c r="D12" s="60" t="s">
+        <v>847</v>
+      </c>
+      <c r="E12" s="60" t="s">
+        <v>848</v>
+      </c>
+      <c r="F12" s="60" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="59" t="n">
+      <c r="B13" s="61" t="n">
         <v>0.5</v>
       </c>
       <c r="C13" s="33" t="n">
         <f aca="false">'11 Динамика'!$D$8+'11 Динамика'!$D$7/'11 Динамика'!$D$6*(1-EXP(-B13/'11 Динамика'!$D$9))</f>
         <v>0.0638868050056159</v>
       </c>
-      <c r="D13" s="60" t="n">
+      <c r="D13" s="62" t="n">
         <v>0.0638922600857928</v>
       </c>
-      <c r="E13" s="61" t="n">
+      <c r="E13" s="63" t="n">
         <f aca="false">ABS(C13-D13)/D13</f>
         <v>8.53793584632849E-005</v>
       </c>
-      <c r="F13" s="62" t="n">
+      <c r="F13" s="64" t="n">
         <f aca="false">C13/'1 Исходные'!$D$25</f>
         <v>0.31943402502808</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="59" t="n">
+      <c r="B14" s="61" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="33" t="n">
         <f aca="false">'11 Динамика'!$D$8+'11 Динамика'!$D$7/'11 Динамика'!$D$6*(1-EXP(-B14/'11 Динамика'!$D$9))</f>
         <v>0.106900493208145</v>
       </c>
-      <c r="D14" s="60" t="n">
+      <c r="D14" s="62" t="n">
         <v>0.106907955454505</v>
       </c>
-      <c r="E14" s="61" t="n">
+      <c r="E14" s="63" t="n">
         <f aca="false">ABS(C14-D14)/D14</f>
         <v>6.980066477551E-005</v>
       </c>
-      <c r="F14" s="62" t="n">
+      <c r="F14" s="64" t="n">
         <f aca="false">C14/'1 Исходные'!$D$25</f>
         <v>0.534502466040723</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="59" t="n">
+      <c r="B15" s="61" t="n">
         <v>1.5</v>
       </c>
       <c r="C15" s="33" t="n">
         <f aca="false">'11 Динамика'!$D$8+'11 Динамика'!$D$7/'11 Динамика'!$D$6*(1-EXP(-B15/'11 Динамика'!$D$9))</f>
         <v>0.136321249638991</v>
       </c>
-      <c r="D15" s="60" t="n">
+      <c r="D15" s="62" t="n">
         <v>0.136328905592563</v>
       </c>
-      <c r="E15" s="61" t="n">
+      <c r="E15" s="63" t="n">
         <f aca="false">ABS(C15-D15)/D15</f>
         <v>5.6157962529383E-005</v>
       </c>
-      <c r="F15" s="62" t="n">
+      <c r="F15" s="64" t="n">
         <f aca="false">C15/'1 Исходные'!$D$25</f>
         <v>0.681606248194955</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="59" t="n">
+      <c r="B16" s="61" t="n">
         <v>2</v>
       </c>
       <c r="C16" s="33" t="n">
         <f aca="false">'11 Динамика'!$D$8+'11 Динамика'!$D$7/'11 Динамика'!$D$6*(1-EXP(-B16/'11 Динамика'!$D$9))</f>
         <v>0.156444632337253</v>
       </c>
-      <c r="D16" s="60" t="n">
+      <c r="D16" s="62" t="n">
         <v>0.156451614283114</v>
       </c>
-      <c r="E16" s="61" t="n">
+      <c r="E16" s="63" t="n">
         <f aca="false">ABS(C16-D16)/D16</f>
         <v>4.46268700586155E-005</v>
       </c>
-      <c r="F16" s="62" t="n">
+      <c r="F16" s="64" t="n">
         <f aca="false">C16/'1 Исходные'!$D$25</f>
         <v>0.782223161686263</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="59" t="n">
+      <c r="B17" s="61" t="n">
         <v>2.5</v>
       </c>
       <c r="C17" s="33" t="n">
         <f aca="false">'11 Динамика'!$D$8+'11 Динамика'!$D$7/'11 Динамика'!$D$6*(1-EXP(-B17/'11 Динамика'!$D$9))</f>
         <v>0.17020874245361</v>
       </c>
-      <c r="D17" s="60" t="n">
+      <c r="D17" s="62" t="n">
         <v>0.170214711774686</v>
       </c>
-      <c r="E17" s="61" t="n">
+      <c r="E17" s="63" t="n">
         <f aca="false">ABS(C17-D17)/D17</f>
         <v>3.50693604215178E-005</v>
       </c>
-      <c r="F17" s="62" t="n">
+      <c r="F17" s="64" t="n">
         <f aca="false">C17/'1 Исходные'!$D$25</f>
         <v>0.85104371226805</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="59" t="n">
+      <c r="B18" s="61" t="n">
         <v>3</v>
       </c>
       <c r="C18" s="33" t="n">
         <f aca="false">'11 Динамика'!$D$8+'11 Динамика'!$D$7/'11 Динамика'!$D$6*(1-EXP(-B18/'11 Динамика'!$D$9))</f>
         <v>0.179623199761107</v>
       </c>
-      <c r="D18" s="60" t="n">
+      <c r="D18" s="62" t="n">
         <v>0.1796280991807</v>
       </c>
-      <c r="E18" s="61" t="n">
+      <c r="E18" s="63" t="n">
         <f aca="false">ABS(C18-D18)/D18</f>
         <v>2.72753517687003E-005</v>
       </c>
-      <c r="F18" s="62" t="n">
+      <c r="F18" s="64" t="n">
         <f aca="false">C18/'1 Исходные'!$D$25</f>
         <v>0.898115998805535</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="59" t="n">
+      <c r="B19" s="61" t="n">
         <v>3.5</v>
       </c>
       <c r="C19" s="33" t="n">
         <f aca="false">'11 Динамика'!$D$8+'11 Динамика'!$D$7/'11 Динамика'!$D$6*(1-EXP(-B19/'11 Динамика'!$D$9))</f>
         <v>0.186062555857899</v>
       </c>
-      <c r="D19" s="60" t="n">
+      <c r="D19" s="62" t="n">
         <v>0.186066465435822</v>
       </c>
-      <c r="E19" s="61" t="n">
+      <c r="E19" s="63" t="n">
         <f aca="false">ABS(C19-D19)/D19</f>
         <v>2.10117277931869E-005</v>
       </c>
-      <c r="F19" s="62" t="n">
+      <c r="F19" s="64" t="n">
         <f aca="false">C19/'1 Исходные'!$D$25</f>
         <v>0.930312779289496</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="59" t="n">
+      <c r="B20" s="61" t="n">
         <v>4</v>
       </c>
       <c r="C20" s="33" t="n">
         <f aca="false">'11 Динамика'!$D$8+'11 Динамика'!$D$7/'11 Динамика'!$D$6*(1-EXP(-B20/'11 Динамика'!$D$9))</f>
         <v>0.190466984662125</v>
       </c>
-      <c r="D20" s="60" t="n">
+      <c r="D20" s="62" t="n">
         <v>0.190470040710821</v>
       </c>
-      <c r="E20" s="61" t="n">
+      <c r="E20" s="63" t="n">
         <f aca="false">ABS(C20-D20)/D20</f>
         <v>1.60447736780805E-005</v>
       </c>
-      <c r="F20" s="62" t="n">
+      <c r="F20" s="64" t="n">
         <f aca="false">C20/'1 Исходные'!$D$25</f>
         <v>0.952334923310626</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="59" t="n">
+      <c r="B21" s="61" t="n">
         <v>4.5</v>
       </c>
       <c r="C21" s="33" t="n">
         <f aca="false">'11 Динамика'!$D$8+'11 Динамика'!$D$7/'11 Динамика'!$D$6*(1-EXP(-B21/'11 Динамика'!$D$9))</f>
         <v>0.193479551881565</v>
       </c>
-      <c r="D21" s="60" t="n">
+      <c r="D21" s="62" t="n">
         <v>0.193481903415454</v>
       </c>
-      <c r="E21" s="61" t="n">
+      <c r="E21" s="63" t="n">
         <f aca="false">ABS(C21-D21)/D21</f>
         <v>1.21537665696098E-005</v>
       </c>
-      <c r="F21" s="62" t="n">
+      <c r="F21" s="64" t="n">
         <f aca="false">C21/'1 Исходные'!$D$25</f>
         <v>0.967397759407824</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="59" t="n">
+      <c r="B22" s="61" t="n">
         <v>5</v>
       </c>
       <c r="C22" s="33" t="n">
         <f aca="false">'11 Динамика'!$D$8+'11 Динамика'!$D$7/'11 Динамика'!$D$6*(1-EXP(-B22/'11 Динамика'!$D$9))</f>
         <v>0.195540105396003</v>
       </c>
-      <c r="D22" s="60" t="n">
+      <c r="D22" s="62" t="n">
         <v>0.195541892489121</v>
       </c>
-      <c r="E22" s="61" t="n">
+      <c r="E22" s="63" t="n">
         <f aca="false">ABS(C22-D22)/D22</f>
         <v>9.13918288523854E-006</v>
       </c>
-      <c r="F22" s="62" t="n">
+      <c r="F22" s="64" t="n">
         <f aca="false">C22/'1 Исходные'!$D$25</f>
         <v>0.977700526980017</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="59" t="n">
+      <c r="B23" s="61" t="n">
         <v>5.5</v>
       </c>
       <c r="C23" s="33" t="n">
         <f aca="false">'11 Динамика'!$D$8+'11 Динамика'!$D$7/'11 Динамика'!$D$6*(1-EXP(-B23/'11 Динамика'!$D$9))</f>
         <v>0.196949494955336</v>
       </c>
-      <c r="D23" s="60" t="n">
+      <c r="D23" s="62" t="n">
         <v>0.196950839509546</v>
       </c>
-      <c r="E23" s="61" t="n">
+      <c r="E23" s="63" t="n">
         <f aca="false">ABS(C23-D23)/D23</f>
         <v>6.82685188646944E-006</v>
       </c>
-      <c r="F23" s="62" t="n">
+      <c r="F23" s="64" t="n">
         <f aca="false">C23/'1 Исходные'!$D$25</f>
         <v>0.984747474776678</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="59" t="n">
+      <c r="B24" s="61" t="n">
         <v>6</v>
       </c>
       <c r="C24" s="33" t="n">
         <f aca="false">'11 Динамика'!$D$8+'11 Динамика'!$D$7/'11 Динамика'!$D$6*(1-EXP(-B24/'11 Динамика'!$D$9))</f>
         <v>0.197913497547861</v>
       </c>
-      <c r="D24" s="60" t="n">
+      <c r="D24" s="62" t="n">
         <v>0.197914500788988</v>
       </c>
-      <c r="E24" s="61" t="n">
+      <c r="E24" s="63" t="n">
         <f aca="false">ABS(C24-D24)/D24</f>
         <v>5.06906327399108E-006</v>
       </c>
-      <c r="F24" s="62" t="n">
+      <c r="F24" s="64" t="n">
         <f aca="false">C24/'1 Исходные'!$D$25</f>
         <v>0.989567487739303</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="59" t="n">
+      <c r="B25" s="61" t="n">
         <v>6.5</v>
       </c>
       <c r="C25" s="33" t="n">
         <f aca="false">'11 Динамика'!$D$8+'11 Динамика'!$D$7/'11 Динамика'!$D$6*(1-EXP(-B25/'11 Динамика'!$D$9))</f>
         <v>0.198572861733044</v>
       </c>
-      <c r="D25" s="60" t="n">
+      <c r="D25" s="62" t="n">
         <v>0.198573605104504</v>
       </c>
-      <c r="E25" s="61" t="n">
+      <c r="E25" s="63" t="n">
         <f aca="false">ABS(C25-D25)/D25</f>
         <v>3.74355624886664E-006</v>
       </c>
-      <c r="F25" s="62" t="n">
+      <c r="F25" s="64" t="n">
         <f aca="false">C25/'1 Исходные'!$D$25</f>
         <v>0.992864308665218</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="59" t="n">
+      <c r="B26" s="61" t="n">
         <v>7</v>
       </c>
       <c r="C26" s="33" t="n">
         <f aca="false">'11 Динамика'!$D$8+'11 Динамика'!$D$7/'11 Динамика'!$D$6*(1-EXP(-B26/'11 Динамика'!$D$9))</f>
         <v>0.199023857541637</v>
       </c>
-      <c r="D26" s="60" t="n">
+      <c r="D26" s="62" t="n">
         <v>0.199024405098236</v>
       </c>
-      <c r="E26" s="61" t="n">
+      <c r="E26" s="63" t="n">
         <f aca="false">ABS(C26-D26)/D26</f>
         <v>2.75120329206184E-006</v>
       </c>
-      <c r="F26" s="62" t="n">
+      <c r="F26" s="64" t="n">
         <f aca="false">C26/'1 Исходные'!$D$25</f>
         <v>0.995119287708186</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="59" t="n">
+      <c r="B27" s="61" t="n">
         <v>7.5</v>
       </c>
       <c r="C27" s="33" t="n">
         <f aca="false">'11 Динамика'!$D$8+'11 Динамика'!$D$7/'11 Динамика'!$D$6*(1-EXP(-B27/'11 Динамика'!$D$9))</f>
         <v>0.199332332317701</v>
       </c>
-      <c r="D27" s="60" t="n">
+      <c r="D27" s="62" t="n">
         <v>0.199332733582156</v>
       </c>
-      <c r="E27" s="61" t="n">
+      <c r="E27" s="63" t="n">
         <f aca="false">ABS(C27-D27)/D27</f>
         <v>2.01303843763798E-006</v>
       </c>
-      <c r="F27" s="62" t="n">
+      <c r="F27" s="64" t="n">
         <f aca="false">C27/'1 Исходные'!$D$25</f>
         <v>0.996661661588507</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="59" t="n">
+      <c r="B28" s="61" t="n">
         <v>8</v>
       </c>
       <c r="C28" s="33" t="n">
         <f aca="false">'11 Динамика'!$D$8+'11 Динамика'!$D$7/'11 Динамика'!$D$6*(1-EXP(-B28/'11 Динамика'!$D$9))</f>
         <v>0.199543324716421</v>
       </c>
-      <c r="D28" s="60" t="n">
+      <c r="D28" s="62" t="n">
         <v>0.199543617467069</v>
       </c>
-      <c r="E28" s="61" t="n">
+      <c r="E28" s="63" t="n">
         <f aca="false">ABS(C28-D28)/D28</f>
         <v>1.46710103226778E-006</v>
       </c>
-      <c r="F28" s="62" t="n">
+      <c r="F28" s="64" t="n">
         <f aca="false">C28/'1 Исходные'!$D$25</f>
         <v>0.997716623582107</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="10" t="s">
-        <v>821</v>
+        <v>850</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
@@ -12378,7 +12709,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -12667,7 +12998,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
         <v>9</v>
       </c>
@@ -12715,7 +13046,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
         <v>11</v>
       </c>
@@ -12777,7 +13108,7 @@
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
     </row>
-    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
         <v>13</v>
       </c>
@@ -12787,12 +13118,11 @@
       <c r="C21" s="8" t="s">
         <v>596</v>
       </c>
-      <c r="D21" s="18" t="n">
-        <f aca="false">'6 Вентилятор'!$D$38*'1 Исходные'!$D$34/1000</f>
-        <v>15.0590604704643</v>
+      <c r="D21" s="43" t="n">
+        <v>1462.102749</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>563</v>
+        <v>479</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>597</v>
@@ -12801,19 +13131,94 @@
         <v>598</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="10" t="s">
         <v>599</v>
       </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
+    </row>
+    <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="D22" s="43" t="n">
+        <v>880.787279</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="D23" s="43" t="n">
+        <v>2060.948012</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <f aca="false">'7 Тепло'!$D$23*'1 Исходные'!$D$34/1000</f>
+        <v>16.487584096</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="10" t="s">
+        <v>608</v>
+      </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -12822,7 +13227,7 @@
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A20:H20"/>
-    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="B25:H25"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
